--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.135" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.135" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.135.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.135.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0135.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L14: possible duplicated/overlap line with previous line (similarity 83%) :: mortgaged premises may be sold, or that the premises</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0135.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr">
@@ -782,7 +778,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -887,12 +883,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.135" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.135" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -603,18 +603,18 @@
           <t>L76: line starts with digit/letter garbage token | suspicious token(s): 7been (letter/digit mix) | localized OCR phrase divergence vs other OCR: "a been" vs "7been" :: 7been to have stated only the names, dates, and amount</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: comprised, for securing the sum of Â£â€” and interest;</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Câ€”â€”, and an</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 128</t>
@@ -634,7 +634,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L76: line starts with digit/letter garbage token | suspicious token(s): 7been (letter/digit mix) | localized OCR phrase divergence vs other OCR: "a been" vs "7been" :: 7been to have stated only the names, dates, and amount</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The names only of the parties are to be set out, not the sub-</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,14 +670,10 @@
           <t>L84: line starts with digit/letter garbage token | suspicious token(s): 1IN (letter/digit mix) :: 1IN CHANCERY.</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief; pray subpa Ã¦ na.)</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢(And fi</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: •(And fi</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -701,7 +697,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L84: line starts with digit/letter garbage token | suspicious token(s): 1IN (letter/digit mix) :: 1IN CHANCERY.</t>
+          <t>L76: line starts with digit/letter garbage token | suspicious token(s): 7been (letter/digit mix) | localized OCR phrase divergence vs other OCR: "a been" vs "7been" :: 7been to have stated only the names, dates, and amount</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -733,14 +729,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - day of â€”</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: comprised, for securing the sum of Â£â€” and interest ;</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The names only of the parties are to be set out, not the sub-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -752,17 +744,21 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”,the will of -----------,dated the ----------day of</t>
+          <t>L94: punctuation artifact: double/multiple hyphen :: —,the will of -----------,dated the ----------day of</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L84: line starts with digit/letter garbage token | suspicious token(s): 1IN (letter/digit mix) :: 1IN CHANCERY.</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -778,12 +774,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -792,14 +788,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the sum of Â£â€” and interest; and that C. D., the de-</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sum of Â£â€” and interest, and the costs of this suit, and</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • indenture, dated the day of -</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -817,7 +809,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • indenture, dated the day of -</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -847,28 +843,24 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: comprised, for securing the sum of Â£â€” and interest;</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ The names only of the parties are to be set out, not the sub-</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: Â£</t>
+          <t>L77: isolated marker/symbol line :: £</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L100: punctuation artifact: double/multiple hyphen :: the sum of Â£-----and interest; and that C. D., the de-</t>
+          <t>L100: punctuation artifact: double/multiple hyphen :: the sum of £-----and interest; and that C. D., the de-</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -902,16 +894,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief; pray subpa Ã¦ na.)</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (and the assurances hereinafter mentionedâ€”that is to</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -953,16 +937,8 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - day of â€”</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”,the will of -----------,dated the ----------day of</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1004,16 +980,8 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the sum of Â£â€” and interest; and that C. D., the de-</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ indenture, dated the day of -</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1041,12 +1009,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1056,11 +1024,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1089,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1206,7 +1170,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
